--- a/ltt/StructureDefinition-klgateway-ltt-encounter.xlsx
+++ b/ltt/StructureDefinition-klgateway-ltt-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3823" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="586">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-31T13:04:54+02:00</t>
+    <t>2025-10-29T22:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -359,7 +359,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -781,7 +781,19 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
-    <t>http://fhir.kl.dk/ltt/ValueSet/fkgateway-ltt-encounter-class-codes</t>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ActCode"/&gt;
+  &lt;code value="AMB"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Classification of the encounter.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -941,15 +953,6 @@
     <t>inpatient | outpatient | ambulatory | emergency +.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Classification of the encounter.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
-  </si>
-  <si>
     <t>Encounter.classHistory.period</t>
   </si>
   <si>
@@ -1031,7 +1034,7 @@
     <t>Broad categorization of the service that is to be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -1093,7 +1096,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare)
+    <t xml:space="preserve">Reference(EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1119,7 +1122,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1204,7 +1207,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1229,7 +1232,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment)
+    <t xml:space="preserve">Reference(Appointment|4.0.1)
 </t>
   </si>
   <si>
@@ -1369,7 +1372,7 @@
     <t>Reason why the encounter takes place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1387,7 +1390,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -1422,7 +1425,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1453,7 +1456,7 @@
     <t>The type of diagnosis this condition represents.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1475,7 +1478,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account)
+    <t xml:space="preserve">Reference(Account|4.0.1)
 </t>
   </si>
   <si>
@@ -1532,7 +1535,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|Organization)
+    <t xml:space="preserve">Reference(Location|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1557,7 +1560,7 @@
     <t>From where the patient was admitted.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1602,7 +1605,7 @@
     <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -1623,7 +1626,7 @@
     <t>Special courtesies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -1644,7 +1647,7 @@
     <t>Special arrangements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -1680,7 +1683,7 @@
     <t>Discharge Disposition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition|4.0.1</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1716,7 +1719,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1772,7 +1775,7 @@
     <t>Physical form of the location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1787,7 +1790,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1806,7 +1809,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -2139,7 +2142,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="77.984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="83.91796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2154,7 +2157,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="65.46484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.7734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -5398,7 +5401,7 @@
         <v>19</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>19</v>
+        <v>246</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>19</v>
@@ -5413,11 +5416,13 @@
         <v>19</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>19</v>
@@ -5453,21 +5458,21 @@
         <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5576,10 +5581,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5690,10 +5695,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5719,16 +5724,16 @@
         <v>100</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>19</v>
@@ -5777,7 +5782,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5795,21 +5800,21 @@
         <v>19</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5835,13 +5840,13 @@
         <v>146</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5891,7 +5896,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5909,21 +5914,21 @@
         <v>19</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5949,14 +5954,14 @@
         <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -6005,7 +6010,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -6023,21 +6028,21 @@
         <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6063,14 +6068,14 @@
         <v>146</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -6119,7 +6124,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6137,21 +6142,21 @@
         <v>19</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6174,19 +6179,19 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6235,7 +6240,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6253,21 +6258,21 @@
         <v>19</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6293,10 +6298,10 @@
         <v>226</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6347,7 +6352,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6376,10 +6381,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6488,10 +6493,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6602,10 +6607,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6718,10 +6723,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6747,10 +6752,10 @@
         <v>178</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6777,31 +6782,31 @@
         <v>19</v>
       </c>
       <c r="X41" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>86</v>
@@ -7046,7 +7051,7 @@
         <v>311</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>312</v>
@@ -7651,16 +7656,16 @@
         <v>100</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7709,7 +7714,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7727,13 +7732,13 @@
         <v>19</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="50">
@@ -7767,13 +7772,13 @@
         <v>146</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7823,7 +7828,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7841,13 +7846,13 @@
         <v>19</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51">
@@ -7881,14 +7886,14 @@
         <v>106</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -7937,7 +7942,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7955,13 +7960,13 @@
         <v>19</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52">
@@ -7995,14 +8000,14 @@
         <v>146</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8051,7 +8056,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8069,13 +8074,13 @@
         <v>19</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="53">
@@ -8106,19 +8111,19 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -8167,7 +8172,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8185,13 +8190,13 @@
         <v>19</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54">
